--- a/artfynd/A 32717-2024 artfynd.xlsx
+++ b/artfynd/A 32717-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119660121</v>
+        <v>119660252</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521791</v>
+        <v>521790</v>
       </c>
       <c r="R4" t="n">
-        <v>6718484</v>
+        <v>6718470</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1012,6 +1012,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>08:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Små fkr</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119660252</v>
+        <v>119660121</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,25 +1055,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1087,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521790</v>
+        <v>521791</v>
       </c>
       <c r="R5" t="n">
-        <v>6718470</v>
+        <v>6718484</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1133,11 +1138,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>08:06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Små fkr</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 32717-2024 artfynd.xlsx
+++ b/artfynd/A 32717-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119660252</v>
+        <v>119660121</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521790</v>
+        <v>521791</v>
       </c>
       <c r="R4" t="n">
-        <v>6718470</v>
+        <v>6718484</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1012,11 +1012,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>08:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Små fkr</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119660121</v>
+        <v>119660252</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,25 +1050,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1092,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521791</v>
+        <v>521790</v>
       </c>
       <c r="R5" t="n">
-        <v>6718484</v>
+        <v>6718470</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1138,6 +1133,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>08:06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Små fkr</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 32717-2024 artfynd.xlsx
+++ b/artfynd/A 32717-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119660437</v>
+        <v>119660252</v>
       </c>
       <c r="B2" t="n">
         <v>91852</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521760</v>
+        <v>521790</v>
       </c>
       <c r="R2" t="n">
-        <v>6718437</v>
+        <v>6718470</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Små fkr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119660077</v>
+        <v>119660121</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,30 +813,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521807</v>
+        <v>521791</v>
       </c>
       <c r="R3" t="n">
-        <v>6718478</v>
+        <v>6718484</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -880,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119660121</v>
+        <v>119661349</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>4766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,47 +934,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Små-Illingarna, Små-Illingarna, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521791</v>
+        <v>521551</v>
       </c>
       <c r="R4" t="n">
-        <v>6718484</v>
+        <v>6718450</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1001,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Klibbal finns</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119660252</v>
+        <v>119660077</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,26 +1060,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521790</v>
+        <v>521807</v>
       </c>
       <c r="R5" t="n">
-        <v>6718470</v>
+        <v>6718478</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1122,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,12 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Små fkr</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119661349</v>
+        <v>119660437</v>
       </c>
       <c r="B6" t="n">
-        <v>4766</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,39 +1181,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Små-Illingarna, Små-Illingarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521551</v>
+        <v>521760</v>
       </c>
       <c r="R6" t="n">
-        <v>6718450</v>
+        <v>6718437</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1244,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,12 +1259,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Klibbal finns</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 32717-2024 artfynd.xlsx
+++ b/artfynd/A 32717-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119660252</v>
+        <v>119660077</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521790</v>
+        <v>521807</v>
       </c>
       <c r="R2" t="n">
-        <v>6718470</v>
+        <v>6718478</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Små fkr</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1044,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119660077</v>
+        <v>119660252</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,26 +1055,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1093,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521807</v>
+        <v>521790</v>
       </c>
       <c r="R5" t="n">
-        <v>6718478</v>
+        <v>6718470</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1128,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1133,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Små fkr</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 32717-2024 artfynd.xlsx
+++ b/artfynd/A 32717-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119660077</v>
+        <v>119660121</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521807</v>
+        <v>521791</v>
       </c>
       <c r="R2" t="n">
-        <v>6718478</v>
+        <v>6718484</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119660121</v>
+        <v>119660077</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,30 +808,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521791</v>
+        <v>521807</v>
       </c>
       <c r="R3" t="n">
-        <v>6718484</v>
+        <v>6718478</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119661349</v>
+        <v>119660252</v>
       </c>
       <c r="B4" t="n">
-        <v>4766</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,39 +933,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Små-Illingarna, Små-Illingarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521551</v>
+        <v>521790</v>
       </c>
       <c r="R4" t="n">
-        <v>6718450</v>
+        <v>6718470</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -997,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,12 +1011,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Klibbal finns</t>
+          <t>Små fkr</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119660252</v>
+        <v>119661349</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>4766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,43 +1059,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Små-Illingarna, Små-Illingarna, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521790</v>
+        <v>521551</v>
       </c>
       <c r="R5" t="n">
-        <v>6718470</v>
+        <v>6718450</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Små fkr</t>
+          <t>Klibbal finns</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 32717-2024 artfynd.xlsx
+++ b/artfynd/A 32717-2024 artfynd.xlsx
@@ -1289,7 +1289,7 @@
         <v>119660408</v>
       </c>
       <c r="B7" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
